--- a/data/loads.xlsx
+++ b/data/loads.xlsx
@@ -41,7 +41,7 @@
     <t>Bracket</t>
   </si>
   <si>
-    <t>2.0 mm flange</t>
+    <t>3.0 mm flange (PDR action)</t>
   </si>
   <si>
     <t>Fasteners (8)</t>
@@ -562,7 +562,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="4">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="6">
         <f>SUM(B4:B7)</f>
-        <v>1.8600000000000003</v>
+        <v>1.9100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -647,7 +647,7 @@
       </c>
       <c r="C4" s="7">
         <f>'Mass properties'!B8*9.80665*B4</f>
-        <v>218.884428</v>
+        <v>224.768418</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
@@ -662,7 +662,7 @@
       </c>
       <c r="C5" s="7">
         <f>'Mass properties'!B8*9.80665*B5</f>
-        <v>218.884428</v>
+        <v>224.768418</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="C6" s="7">
         <f>'Mass properties'!B8*9.80665*B6</f>
-        <v>328.326642</v>
+        <v>337.152627</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
